--- a/public/Template - WashLi Laundry Services.xlsx
+++ b/public/Template - WashLi Laundry Services.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vgpan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF54E27-946B-440F-808E-3E5591F452C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23858109-4EB8-4147-BDCC-9C663850CE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Item Code</t>
   </si>
@@ -200,13 +201,37 @@
   </si>
   <si>
     <t>Socks, briefs, etc.</t>
+  </si>
+  <si>
+    <t>Item Photo (Example Data)</t>
+  </si>
+  <si>
+    <t>[Cell shows a placeholder image of a neatly folded shirt with instructions "Insert Photo"]</t>
+  </si>
+  <si>
+    <t>Standard button-down</t>
+  </si>
+  <si>
+    <t>[Placeholder Image]</t>
+  </si>
+  <si>
+    <t>LND-4001</t>
+  </si>
+  <si>
+    <t>Bedsheet</t>
+  </si>
+  <si>
+    <t>King size</t>
+  </si>
+  <si>
+    <t>Household</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -228,8 +253,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,6 +278,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,8 +321,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -290,10 +353,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -557,7 +623,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -588,7 +654,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>19</v>
       </c>
@@ -650,7 +716,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>32</v>
       </c>
@@ -797,7 +863,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>56</v>
       </c>
@@ -827,6 +893,339 @@
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C403151A-0D7B-4BD9-988F-33E409BD5913}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
